--- a/Gearbox_DaughterBoard/CPL.xlsx
+++ b/Gearbox_DaughterBoard/CPL.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_DBB_2026-04-16" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_DBB_2026_06_13" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="72">
   <si>
     <t>Designator</t>
   </si>
@@ -55,13 +55,16 @@
     <t>Comment</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
     <t>C2</t>
   </si>
   <si>
-    <t>CC0603KRX7R9BB104</t>
-  </si>
-  <si>
-    <t>C0603</t>
+    <t>CL05B104KB54PNC</t>
+  </si>
+  <si>
+    <t>C0402</t>
   </si>
   <si>
     <t>-19.05mm</t>
@@ -70,7 +73,7 @@
     <t>7.62mm</t>
   </si>
   <si>
-    <t>-19.75mm</t>
+    <t>-19.47mm</t>
   </si>
   <si>
     <t>T</t>
@@ -91,37 +94,64 @@
     <t>36.703mm</t>
   </si>
   <si>
-    <t>-2.605mm</t>
+    <t>-2.325mm</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>0402WGF1001TCE</t>
+  </si>
+  <si>
+    <t>R0402</t>
+  </si>
+  <si>
+    <t>5.588mm</t>
+  </si>
+  <si>
+    <t>-19.483mm</t>
+  </si>
+  <si>
+    <t>1kΩ</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>38.481mm</t>
+  </si>
+  <si>
+    <t>-2.338mm</t>
   </si>
   <si>
     <t>CN6</t>
   </si>
   <si>
-    <t>SH1.0mm-2P-LT</t>
-  </si>
-  <si>
-    <t>CONN-SMD_SH1.0MM-2P-LT</t>
+    <t>S2B-ZR-SM2-TF(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN-SMD_2P-P1.50_S2B-ZR-SM2-TF-LF-SN</t>
   </si>
   <si>
     <t>-18.542mm</t>
   </si>
   <si>
-    <t>18.669mm</t>
-  </si>
-  <si>
-    <t>-19.042mm</t>
-  </si>
-  <si>
-    <t>20.007mm</t>
+    <t>20.066mm</t>
+  </si>
+  <si>
+    <t>-19.292mm</t>
   </si>
   <si>
     <t>CN9</t>
   </si>
   <si>
-    <t>-3.429mm</t>
-  </si>
-  <si>
-    <t>-3.929mm</t>
+    <t>-3.556mm</t>
+  </si>
+  <si>
+    <t>20.193mm</t>
+  </si>
+  <si>
+    <t>-4.306mm</t>
   </si>
   <si>
     <t>CN10</t>
@@ -130,7 +160,7 @@
     <t>-13.589mm</t>
   </si>
   <si>
-    <t>-14.089mm</t>
+    <t>-14.339mm</t>
   </si>
   <si>
     <t>CN11</t>
@@ -139,7 +169,7 @@
     <t>-8.636mm</t>
   </si>
   <si>
-    <t>-9.136mm</t>
+    <t>-9.386mm</t>
   </si>
   <si>
     <t>CN12</t>
@@ -161,33 +191,6 @@
   </si>
   <si>
     <t>7.031mm</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>FRC0603J102 TS</t>
-  </si>
-  <si>
-    <t>R0603</t>
-  </si>
-  <si>
-    <t>5.588mm</t>
-  </si>
-  <si>
-    <t>-19.803mm</t>
-  </si>
-  <si>
-    <t>1kΩ</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>38.481mm</t>
-  </si>
-  <si>
-    <t>-2.658mm</t>
   </si>
   <si>
     <t>U2</t>
@@ -600,13 +603,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="14" width="20" customWidth="1"/>
+    <col min="1" max="15" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -649,113 +652,122 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
         <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
       </c>
       <c r="J2">
         <v>2</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
         <v>26</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="O3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
         <v>31</v>
@@ -764,262 +776,280 @@
         <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N4" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="O4" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
         <v>35</v>
       </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
       <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
         <v>35</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
       </c>
       <c r="H5" t="s">
         <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N5" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="O5" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7" t="s">
         <v>21</v>
-      </c>
-      <c r="N6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7" t="s">
-        <v>20</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" t="s">
+        <v>38</v>
+      </c>
+      <c r="O7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8" t="s">
         <v>21</v>
       </c>
-      <c r="N7" t="s">
-        <v>28</v>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O8" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8">
-        <v>10</v>
-      </c>
-      <c r="K8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>180</v>
-      </c>
-      <c r="M8" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>50</v>
       </c>
       <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
         <v>51</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" t="s">
         <v>52</v>
       </c>
-      <c r="D9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" t="s">
-        <v>54</v>
-      </c>
       <c r="I9" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="J9">
         <v>2</v>
       </c>
       <c r="K9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="D10" t="s">
         <v>56</v>
-      </c>
-      <c r="B10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
       </c>
       <c r="E10" t="s">
         <v>57</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="G10" t="s">
         <v>57</v>
@@ -1028,110 +1058,119 @@
         <v>58</v>
       </c>
       <c r="I10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N10" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="O10" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s">
         <v>63</v>
       </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
       <c r="G11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J11">
         <v>3</v>
       </c>
       <c r="K11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N11" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="O11" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s">
         <v>68</v>
       </c>
-      <c r="F12" t="s">
-        <v>67</v>
-      </c>
       <c r="G12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J12">
         <v>3</v>
       </c>
       <c r="K12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L12">
         <v>270</v>
       </c>
       <c r="M12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N12" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="O12" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
